--- a/data/dataframe/10014.xlsx
+++ b/data/dataframe/10014.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10112"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tug83224/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shujie/jlab/CJ/CJ-database/data/dataframe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA436FDD-815D-ED4A-93D6-D09C8F4BDE7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7D5CA0B-8854-3840-8137-0B5B7E45D74E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="29160" windowHeight="17000" tabRatio="993" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="format" sheetId="2" r:id="rId1"/>
     <sheet name="old" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="181029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -25,7 +25,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6656" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6656" uniqueCount="42">
   <si>
     <t>Elab</t>
   </si>
@@ -160,9 +159,6 @@
   </si>
   <si>
     <t>slac</t>
-  </si>
-  <si>
-    <t>f</t>
   </si>
   <si>
     <t>e_minus</t>
@@ -700,7 +696,7 @@
         <v>13</v>
       </c>
       <c r="K2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L2" t="s">
         <v>16</v>
@@ -801,7 +797,7 @@
         <v>13</v>
       </c>
       <c r="K3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L3" t="s">
         <v>16</v>
@@ -902,7 +898,7 @@
         <v>13</v>
       </c>
       <c r="K4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L4" t="s">
         <v>16</v>
@@ -1003,7 +999,7 @@
         <v>13</v>
       </c>
       <c r="K5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L5" t="s">
         <v>16</v>
@@ -1104,7 +1100,7 @@
         <v>13</v>
       </c>
       <c r="K6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L6" t="s">
         <v>16</v>
@@ -1205,7 +1201,7 @@
         <v>13</v>
       </c>
       <c r="K7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L7" t="s">
         <v>16</v>
@@ -1306,7 +1302,7 @@
         <v>13</v>
       </c>
       <c r="K8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L8" t="s">
         <v>16</v>
@@ -1407,7 +1403,7 @@
         <v>13</v>
       </c>
       <c r="K9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L9" t="s">
         <v>16</v>
@@ -1508,7 +1504,7 @@
         <v>13</v>
       </c>
       <c r="K10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L10" t="s">
         <v>16</v>
@@ -1609,7 +1605,7 @@
         <v>13</v>
       </c>
       <c r="K11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L11" t="s">
         <v>16</v>
@@ -1710,7 +1706,7 @@
         <v>13</v>
       </c>
       <c r="K12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L12" t="s">
         <v>16</v>
@@ -1811,7 +1807,7 @@
         <v>13</v>
       </c>
       <c r="K13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L13" t="s">
         <v>16</v>
@@ -1912,7 +1908,7 @@
         <v>13</v>
       </c>
       <c r="K14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L14" t="s">
         <v>16</v>
@@ -2013,7 +2009,7 @@
         <v>13</v>
       </c>
       <c r="K15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L15" t="s">
         <v>16</v>
@@ -2114,7 +2110,7 @@
         <v>13</v>
       </c>
       <c r="K16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L16" t="s">
         <v>16</v>
@@ -2215,7 +2211,7 @@
         <v>13</v>
       </c>
       <c r="K17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L17" t="s">
         <v>16</v>
@@ -2316,7 +2312,7 @@
         <v>13</v>
       </c>
       <c r="K18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L18" t="s">
         <v>16</v>
@@ -2417,7 +2413,7 @@
         <v>13</v>
       </c>
       <c r="K19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L19" t="s">
         <v>16</v>
@@ -2518,7 +2514,7 @@
         <v>13</v>
       </c>
       <c r="K20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L20" t="s">
         <v>16</v>
@@ -2619,7 +2615,7 @@
         <v>13</v>
       </c>
       <c r="K21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L21" t="s">
         <v>16</v>
@@ -2720,7 +2716,7 @@
         <v>13</v>
       </c>
       <c r="K22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L22" t="s">
         <v>16</v>
@@ -2821,7 +2817,7 @@
         <v>13</v>
       </c>
       <c r="K23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L23" t="s">
         <v>16</v>
@@ -2922,7 +2918,7 @@
         <v>13</v>
       </c>
       <c r="K24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L24" t="s">
         <v>16</v>
@@ -3023,7 +3019,7 @@
         <v>13</v>
       </c>
       <c r="K25" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L25" t="s">
         <v>16</v>
@@ -3124,7 +3120,7 @@
         <v>13</v>
       </c>
       <c r="K26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L26" t="s">
         <v>16</v>
@@ -3225,7 +3221,7 @@
         <v>13</v>
       </c>
       <c r="K27" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L27" t="s">
         <v>16</v>
@@ -3326,7 +3322,7 @@
         <v>13</v>
       </c>
       <c r="K28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L28" t="s">
         <v>16</v>
@@ -3427,7 +3423,7 @@
         <v>13</v>
       </c>
       <c r="K29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L29" t="s">
         <v>16</v>
@@ -3528,7 +3524,7 @@
         <v>13</v>
       </c>
       <c r="K30" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L30" t="s">
         <v>16</v>
@@ -3629,7 +3625,7 @@
         <v>13</v>
       </c>
       <c r="K31" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L31" t="s">
         <v>16</v>
@@ -3730,7 +3726,7 @@
         <v>13</v>
       </c>
       <c r="K32" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L32" t="s">
         <v>16</v>
@@ -3831,7 +3827,7 @@
         <v>13</v>
       </c>
       <c r="K33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L33" t="s">
         <v>16</v>
@@ -3932,7 +3928,7 @@
         <v>13</v>
       </c>
       <c r="K34" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L34" t="s">
         <v>16</v>
@@ -4033,7 +4029,7 @@
         <v>13</v>
       </c>
       <c r="K35" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L35" t="s">
         <v>16</v>
@@ -4134,7 +4130,7 @@
         <v>13</v>
       </c>
       <c r="K36" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L36" t="s">
         <v>16</v>
@@ -4235,7 +4231,7 @@
         <v>13</v>
       </c>
       <c r="K37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L37" t="s">
         <v>16</v>
@@ -4336,7 +4332,7 @@
         <v>13</v>
       </c>
       <c r="K38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L38" t="s">
         <v>16</v>
@@ -4437,7 +4433,7 @@
         <v>13</v>
       </c>
       <c r="K39" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L39" t="s">
         <v>16</v>
@@ -4538,7 +4534,7 @@
         <v>13</v>
       </c>
       <c r="K40" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L40" t="s">
         <v>16</v>
@@ -4639,7 +4635,7 @@
         <v>13</v>
       </c>
       <c r="K41" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L41" t="s">
         <v>16</v>
@@ -4740,7 +4736,7 @@
         <v>13</v>
       </c>
       <c r="K42" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L42" t="s">
         <v>16</v>
@@ -4841,7 +4837,7 @@
         <v>13</v>
       </c>
       <c r="K43" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L43" t="s">
         <v>16</v>
@@ -4942,7 +4938,7 @@
         <v>13</v>
       </c>
       <c r="K44" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L44" t="s">
         <v>16</v>
@@ -5043,7 +5039,7 @@
         <v>13</v>
       </c>
       <c r="K45" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L45" t="s">
         <v>16</v>
@@ -5144,7 +5140,7 @@
         <v>13</v>
       </c>
       <c r="K46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L46" t="s">
         <v>16</v>
@@ -5245,7 +5241,7 @@
         <v>13</v>
       </c>
       <c r="K47" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L47" t="s">
         <v>16</v>
@@ -5346,7 +5342,7 @@
         <v>13</v>
       </c>
       <c r="K48" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L48" t="s">
         <v>16</v>
@@ -5447,7 +5443,7 @@
         <v>13</v>
       </c>
       <c r="K49" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L49" t="s">
         <v>16</v>
@@ -5548,7 +5544,7 @@
         <v>13</v>
       </c>
       <c r="K50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L50" t="s">
         <v>16</v>
@@ -5649,7 +5645,7 @@
         <v>13</v>
       </c>
       <c r="K51" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L51" t="s">
         <v>16</v>
@@ -5750,7 +5746,7 @@
         <v>13</v>
       </c>
       <c r="K52" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L52" t="s">
         <v>16</v>
@@ -5851,7 +5847,7 @@
         <v>13</v>
       </c>
       <c r="K53" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L53" t="s">
         <v>16</v>
@@ -5952,7 +5948,7 @@
         <v>13</v>
       </c>
       <c r="K54" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L54" t="s">
         <v>16</v>
@@ -6053,7 +6049,7 @@
         <v>13</v>
       </c>
       <c r="K55" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L55" t="s">
         <v>16</v>
@@ -6154,7 +6150,7 @@
         <v>13</v>
       </c>
       <c r="K56" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L56" t="s">
         <v>16</v>
@@ -6255,7 +6251,7 @@
         <v>13</v>
       </c>
       <c r="K57" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L57" t="s">
         <v>16</v>
@@ -6356,7 +6352,7 @@
         <v>13</v>
       </c>
       <c r="K58" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L58" t="s">
         <v>16</v>
@@ -6457,7 +6453,7 @@
         <v>13</v>
       </c>
       <c r="K59" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L59" t="s">
         <v>16</v>
@@ -6558,7 +6554,7 @@
         <v>13</v>
       </c>
       <c r="K60" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L60" t="s">
         <v>16</v>
@@ -6659,7 +6655,7 @@
         <v>13</v>
       </c>
       <c r="K61" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L61" t="s">
         <v>16</v>
@@ -6760,7 +6756,7 @@
         <v>13</v>
       </c>
       <c r="K62" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L62" t="s">
         <v>16</v>
@@ -6861,7 +6857,7 @@
         <v>13</v>
       </c>
       <c r="K63" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L63" t="s">
         <v>16</v>
@@ -6962,7 +6958,7 @@
         <v>13</v>
       </c>
       <c r="K64" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L64" t="s">
         <v>16</v>
@@ -7063,7 +7059,7 @@
         <v>13</v>
       </c>
       <c r="K65" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L65" t="s">
         <v>16</v>
@@ -7164,7 +7160,7 @@
         <v>13</v>
       </c>
       <c r="K66" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L66" t="s">
         <v>16</v>
@@ -7265,7 +7261,7 @@
         <v>13</v>
       </c>
       <c r="K67" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L67" t="s">
         <v>16</v>
@@ -7366,7 +7362,7 @@
         <v>13</v>
       </c>
       <c r="K68" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L68" t="s">
         <v>16</v>
@@ -7467,7 +7463,7 @@
         <v>13</v>
       </c>
       <c r="K69" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L69" t="s">
         <v>16</v>
@@ -7568,7 +7564,7 @@
         <v>13</v>
       </c>
       <c r="K70" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L70" t="s">
         <v>16</v>
@@ -7669,7 +7665,7 @@
         <v>13</v>
       </c>
       <c r="K71" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L71" t="s">
         <v>16</v>
@@ -7770,7 +7766,7 @@
         <v>13</v>
       </c>
       <c r="K72" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L72" t="s">
         <v>16</v>
@@ -7871,7 +7867,7 @@
         <v>13</v>
       </c>
       <c r="K73" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L73" t="s">
         <v>16</v>
@@ -7972,7 +7968,7 @@
         <v>13</v>
       </c>
       <c r="K74" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L74" t="s">
         <v>16</v>
@@ -8073,7 +8069,7 @@
         <v>13</v>
       </c>
       <c r="K75" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L75" t="s">
         <v>16</v>
@@ -8174,7 +8170,7 @@
         <v>13</v>
       </c>
       <c r="K76" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L76" t="s">
         <v>16</v>
@@ -8275,7 +8271,7 @@
         <v>13</v>
       </c>
       <c r="K77" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L77" t="s">
         <v>16</v>
@@ -8376,7 +8372,7 @@
         <v>13</v>
       </c>
       <c r="K78" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L78" t="s">
         <v>16</v>
@@ -8477,7 +8473,7 @@
         <v>13</v>
       </c>
       <c r="K79" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L79" t="s">
         <v>16</v>
@@ -8578,7 +8574,7 @@
         <v>13</v>
       </c>
       <c r="K80" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L80" t="s">
         <v>16</v>
@@ -8679,7 +8675,7 @@
         <v>13</v>
       </c>
       <c r="K81" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L81" t="s">
         <v>16</v>
@@ -8780,7 +8776,7 @@
         <v>13</v>
       </c>
       <c r="K82" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L82" t="s">
         <v>16</v>
@@ -8881,7 +8877,7 @@
         <v>13</v>
       </c>
       <c r="K83" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L83" t="s">
         <v>16</v>
@@ -8982,7 +8978,7 @@
         <v>13</v>
       </c>
       <c r="K84" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L84" t="s">
         <v>16</v>
@@ -9083,7 +9079,7 @@
         <v>13</v>
       </c>
       <c r="K85" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L85" t="s">
         <v>16</v>
@@ -9184,7 +9180,7 @@
         <v>13</v>
       </c>
       <c r="K86" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L86" t="s">
         <v>16</v>
@@ -9285,7 +9281,7 @@
         <v>13</v>
       </c>
       <c r="K87" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L87" t="s">
         <v>16</v>
@@ -9386,7 +9382,7 @@
         <v>13</v>
       </c>
       <c r="K88" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L88" t="s">
         <v>16</v>
@@ -9487,7 +9483,7 @@
         <v>13</v>
       </c>
       <c r="K89" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L89" t="s">
         <v>16</v>
@@ -9588,7 +9584,7 @@
         <v>13</v>
       </c>
       <c r="K90" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L90" t="s">
         <v>16</v>
@@ -9689,7 +9685,7 @@
         <v>13</v>
       </c>
       <c r="K91" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L91" t="s">
         <v>16</v>
@@ -9790,7 +9786,7 @@
         <v>13</v>
       </c>
       <c r="K92" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L92" t="s">
         <v>16</v>
@@ -9891,7 +9887,7 @@
         <v>13</v>
       </c>
       <c r="K93" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L93" t="s">
         <v>16</v>
@@ -9992,7 +9988,7 @@
         <v>13</v>
       </c>
       <c r="K94" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L94" t="s">
         <v>16</v>
@@ -10093,7 +10089,7 @@
         <v>13</v>
       </c>
       <c r="K95" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L95" t="s">
         <v>16</v>
@@ -10194,7 +10190,7 @@
         <v>13</v>
       </c>
       <c r="K96" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L96" t="s">
         <v>16</v>
@@ -10295,7 +10291,7 @@
         <v>13</v>
       </c>
       <c r="K97" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L97" t="s">
         <v>16</v>
@@ -10396,7 +10392,7 @@
         <v>13</v>
       </c>
       <c r="K98" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L98" t="s">
         <v>16</v>
@@ -10497,7 +10493,7 @@
         <v>13</v>
       </c>
       <c r="K99" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L99" t="s">
         <v>16</v>
@@ -10598,7 +10594,7 @@
         <v>13</v>
       </c>
       <c r="K100" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L100" t="s">
         <v>16</v>
@@ -10699,7 +10695,7 @@
         <v>13</v>
       </c>
       <c r="K101" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L101" t="s">
         <v>16</v>
@@ -10800,7 +10796,7 @@
         <v>13</v>
       </c>
       <c r="K102" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L102" t="s">
         <v>16</v>
@@ -10901,7 +10897,7 @@
         <v>13</v>
       </c>
       <c r="K103" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L103" t="s">
         <v>16</v>
@@ -11002,7 +10998,7 @@
         <v>13</v>
       </c>
       <c r="K104" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L104" t="s">
         <v>16</v>
@@ -11103,7 +11099,7 @@
         <v>13</v>
       </c>
       <c r="K105" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L105" t="s">
         <v>16</v>
@@ -11204,7 +11200,7 @@
         <v>13</v>
       </c>
       <c r="K106" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L106" t="s">
         <v>16</v>
@@ -11305,7 +11301,7 @@
         <v>13</v>
       </c>
       <c r="K107" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L107" t="s">
         <v>16</v>
@@ -11406,7 +11402,7 @@
         <v>13</v>
       </c>
       <c r="K108" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L108" t="s">
         <v>16</v>
@@ -11507,7 +11503,7 @@
         <v>13</v>
       </c>
       <c r="K109" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L109" t="s">
         <v>16</v>
@@ -11608,7 +11604,7 @@
         <v>13</v>
       </c>
       <c r="K110" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L110" t="s">
         <v>16</v>
@@ -11709,7 +11705,7 @@
         <v>13</v>
       </c>
       <c r="K111" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L111" t="s">
         <v>16</v>
@@ -11810,7 +11806,7 @@
         <v>13</v>
       </c>
       <c r="K112" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L112" t="s">
         <v>16</v>
@@ -11911,7 +11907,7 @@
         <v>13</v>
       </c>
       <c r="K113" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L113" t="s">
         <v>16</v>
@@ -12012,7 +12008,7 @@
         <v>13</v>
       </c>
       <c r="K114" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L114" t="s">
         <v>16</v>
@@ -12113,7 +12109,7 @@
         <v>13</v>
       </c>
       <c r="K115" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L115" t="s">
         <v>16</v>
@@ -12214,7 +12210,7 @@
         <v>13</v>
       </c>
       <c r="K116" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L116" t="s">
         <v>16</v>
@@ -12315,7 +12311,7 @@
         <v>13</v>
       </c>
       <c r="K117" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L117" t="s">
         <v>16</v>
@@ -12416,7 +12412,7 @@
         <v>13</v>
       </c>
       <c r="K118" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L118" t="s">
         <v>16</v>
@@ -12517,7 +12513,7 @@
         <v>13</v>
       </c>
       <c r="K119" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L119" t="s">
         <v>16</v>
@@ -12618,7 +12614,7 @@
         <v>13</v>
       </c>
       <c r="K120" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L120" t="s">
         <v>16</v>
@@ -12719,7 +12715,7 @@
         <v>13</v>
       </c>
       <c r="K121" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L121" t="s">
         <v>16</v>
@@ -12820,7 +12816,7 @@
         <v>13</v>
       </c>
       <c r="K122" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L122" t="s">
         <v>16</v>
@@ -12921,7 +12917,7 @@
         <v>13</v>
       </c>
       <c r="K123" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L123" t="s">
         <v>16</v>
@@ -13022,7 +13018,7 @@
         <v>13</v>
       </c>
       <c r="K124" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L124" t="s">
         <v>16</v>
@@ -13123,7 +13119,7 @@
         <v>13</v>
       </c>
       <c r="K125" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L125" t="s">
         <v>16</v>
@@ -13224,7 +13220,7 @@
         <v>13</v>
       </c>
       <c r="K126" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L126" t="s">
         <v>16</v>
@@ -13325,7 +13321,7 @@
         <v>13</v>
       </c>
       <c r="K127" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L127" t="s">
         <v>16</v>
@@ -13426,7 +13422,7 @@
         <v>13</v>
       </c>
       <c r="K128" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L128" t="s">
         <v>16</v>
@@ -13527,7 +13523,7 @@
         <v>13</v>
       </c>
       <c r="K129" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L129" t="s">
         <v>16</v>
@@ -13628,7 +13624,7 @@
         <v>13</v>
       </c>
       <c r="K130" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L130" t="s">
         <v>16</v>
@@ -13729,7 +13725,7 @@
         <v>13</v>
       </c>
       <c r="K131" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L131" t="s">
         <v>16</v>
@@ -13830,7 +13826,7 @@
         <v>13</v>
       </c>
       <c r="K132" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L132" t="s">
         <v>16</v>
@@ -13931,7 +13927,7 @@
         <v>13</v>
       </c>
       <c r="K133" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L133" t="s">
         <v>16</v>
@@ -14032,7 +14028,7 @@
         <v>13</v>
       </c>
       <c r="K134" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L134" t="s">
         <v>16</v>
@@ -14133,7 +14129,7 @@
         <v>13</v>
       </c>
       <c r="K135" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L135" t="s">
         <v>16</v>
@@ -14234,7 +14230,7 @@
         <v>13</v>
       </c>
       <c r="K136" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L136" t="s">
         <v>16</v>
@@ -14335,7 +14331,7 @@
         <v>13</v>
       </c>
       <c r="K137" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L137" t="s">
         <v>16</v>
@@ -14436,7 +14432,7 @@
         <v>13</v>
       </c>
       <c r="K138" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L138" t="s">
         <v>16</v>
@@ -14537,7 +14533,7 @@
         <v>13</v>
       </c>
       <c r="K139" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L139" t="s">
         <v>16</v>
@@ -14638,7 +14634,7 @@
         <v>13</v>
       </c>
       <c r="K140" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L140" t="s">
         <v>16</v>
@@ -14739,7 +14735,7 @@
         <v>13</v>
       </c>
       <c r="K141" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L141" t="s">
         <v>16</v>
@@ -14840,7 +14836,7 @@
         <v>13</v>
       </c>
       <c r="K142" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L142" t="s">
         <v>16</v>
@@ -14941,7 +14937,7 @@
         <v>13</v>
       </c>
       <c r="K143" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L143" t="s">
         <v>16</v>
@@ -15042,7 +15038,7 @@
         <v>13</v>
       </c>
       <c r="K144" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L144" t="s">
         <v>16</v>
@@ -15143,7 +15139,7 @@
         <v>13</v>
       </c>
       <c r="K145" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L145" t="s">
         <v>16</v>
@@ -15244,7 +15240,7 @@
         <v>13</v>
       </c>
       <c r="K146" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L146" t="s">
         <v>16</v>
@@ -15345,7 +15341,7 @@
         <v>13</v>
       </c>
       <c r="K147" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L147" t="s">
         <v>16</v>
@@ -15446,7 +15442,7 @@
         <v>13</v>
       </c>
       <c r="K148" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L148" t="s">
         <v>16</v>
@@ -15547,7 +15543,7 @@
         <v>13</v>
       </c>
       <c r="K149" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L149" t="s">
         <v>16</v>
@@ -15648,7 +15644,7 @@
         <v>13</v>
       </c>
       <c r="K150" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L150" t="s">
         <v>16</v>
@@ -15749,7 +15745,7 @@
         <v>13</v>
       </c>
       <c r="K151" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L151" t="s">
         <v>16</v>
@@ -15850,7 +15846,7 @@
         <v>13</v>
       </c>
       <c r="K152" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L152" t="s">
         <v>16</v>
@@ -15951,7 +15947,7 @@
         <v>13</v>
       </c>
       <c r="K153" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L153" t="s">
         <v>16</v>
@@ -16052,7 +16048,7 @@
         <v>13</v>
       </c>
       <c r="K154" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L154" t="s">
         <v>16</v>
@@ -16153,7 +16149,7 @@
         <v>13</v>
       </c>
       <c r="K155" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L155" t="s">
         <v>16</v>
@@ -16254,7 +16250,7 @@
         <v>13</v>
       </c>
       <c r="K156" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L156" t="s">
         <v>16</v>
@@ -16355,7 +16351,7 @@
         <v>13</v>
       </c>
       <c r="K157" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L157" t="s">
         <v>16</v>
@@ -16456,7 +16452,7 @@
         <v>13</v>
       </c>
       <c r="K158" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L158" t="s">
         <v>16</v>
@@ -16557,7 +16553,7 @@
         <v>13</v>
       </c>
       <c r="K159" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L159" t="s">
         <v>16</v>
@@ -16658,7 +16654,7 @@
         <v>13</v>
       </c>
       <c r="K160" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L160" t="s">
         <v>16</v>
@@ -16759,7 +16755,7 @@
         <v>13</v>
       </c>
       <c r="K161" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L161" t="s">
         <v>16</v>
@@ -16860,7 +16856,7 @@
         <v>13</v>
       </c>
       <c r="K162" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L162" t="s">
         <v>16</v>
@@ -16961,7 +16957,7 @@
         <v>13</v>
       </c>
       <c r="K163" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L163" t="s">
         <v>16</v>
@@ -17062,7 +17058,7 @@
         <v>13</v>
       </c>
       <c r="K164" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L164" t="s">
         <v>16</v>
@@ -17163,7 +17159,7 @@
         <v>13</v>
       </c>
       <c r="K165" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L165" t="s">
         <v>16</v>
@@ -17264,7 +17260,7 @@
         <v>13</v>
       </c>
       <c r="K166" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L166" t="s">
         <v>16</v>
@@ -17365,7 +17361,7 @@
         <v>13</v>
       </c>
       <c r="K167" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L167" t="s">
         <v>16</v>
@@ -17466,7 +17462,7 @@
         <v>13</v>
       </c>
       <c r="K168" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L168" t="s">
         <v>16</v>
@@ -17567,7 +17563,7 @@
         <v>13</v>
       </c>
       <c r="K169" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L169" t="s">
         <v>16</v>
@@ -17668,7 +17664,7 @@
         <v>13</v>
       </c>
       <c r="K170" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L170" t="s">
         <v>16</v>
@@ -17769,7 +17765,7 @@
         <v>13</v>
       </c>
       <c r="K171" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L171" t="s">
         <v>16</v>
@@ -17870,7 +17866,7 @@
         <v>13</v>
       </c>
       <c r="K172" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L172" t="s">
         <v>16</v>
@@ -17971,7 +17967,7 @@
         <v>13</v>
       </c>
       <c r="K173" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L173" t="s">
         <v>16</v>
@@ -18072,7 +18068,7 @@
         <v>13</v>
       </c>
       <c r="K174" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L174" t="s">
         <v>16</v>
@@ -18173,7 +18169,7 @@
         <v>13</v>
       </c>
       <c r="K175" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L175" t="s">
         <v>16</v>
@@ -18274,7 +18270,7 @@
         <v>13</v>
       </c>
       <c r="K176" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L176" t="s">
         <v>16</v>
@@ -18375,7 +18371,7 @@
         <v>13</v>
       </c>
       <c r="K177" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L177" t="s">
         <v>16</v>
@@ -18476,7 +18472,7 @@
         <v>13</v>
       </c>
       <c r="K178" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L178" t="s">
         <v>16</v>
@@ -18577,7 +18573,7 @@
         <v>13</v>
       </c>
       <c r="K179" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L179" t="s">
         <v>16</v>
@@ -18678,7 +18674,7 @@
         <v>13</v>
       </c>
       <c r="K180" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L180" t="s">
         <v>16</v>
@@ -18779,7 +18775,7 @@
         <v>13</v>
       </c>
       <c r="K181" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L181" t="s">
         <v>16</v>
@@ -18880,7 +18876,7 @@
         <v>13</v>
       </c>
       <c r="K182" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L182" t="s">
         <v>16</v>
@@ -18981,7 +18977,7 @@
         <v>13</v>
       </c>
       <c r="K183" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L183" t="s">
         <v>16</v>
@@ -19082,7 +19078,7 @@
         <v>13</v>
       </c>
       <c r="K184" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L184" t="s">
         <v>16</v>
@@ -19183,7 +19179,7 @@
         <v>13</v>
       </c>
       <c r="K185" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L185" t="s">
         <v>16</v>
@@ -19284,7 +19280,7 @@
         <v>13</v>
       </c>
       <c r="K186" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L186" t="s">
         <v>16</v>
@@ -19385,7 +19381,7 @@
         <v>13</v>
       </c>
       <c r="K187" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L187" t="s">
         <v>16</v>
@@ -19486,7 +19482,7 @@
         <v>13</v>
       </c>
       <c r="K188" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L188" t="s">
         <v>16</v>
@@ -19587,7 +19583,7 @@
         <v>13</v>
       </c>
       <c r="K189" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L189" t="s">
         <v>16</v>
@@ -19688,7 +19684,7 @@
         <v>13</v>
       </c>
       <c r="K190" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L190" t="s">
         <v>16</v>
@@ -19789,7 +19785,7 @@
         <v>13</v>
       </c>
       <c r="K191" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L191" t="s">
         <v>16</v>
@@ -19890,7 +19886,7 @@
         <v>13</v>
       </c>
       <c r="K192" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L192" t="s">
         <v>16</v>
@@ -19991,7 +19987,7 @@
         <v>13</v>
       </c>
       <c r="K193" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L193" t="s">
         <v>16</v>
@@ -20092,7 +20088,7 @@
         <v>13</v>
       </c>
       <c r="K194" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L194" t="s">
         <v>16</v>
@@ -20193,7 +20189,7 @@
         <v>13</v>
       </c>
       <c r="K195" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L195" t="s">
         <v>16</v>
@@ -20294,7 +20290,7 @@
         <v>13</v>
       </c>
       <c r="K196" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L196" t="s">
         <v>16</v>
@@ -20395,7 +20391,7 @@
         <v>13</v>
       </c>
       <c r="K197" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L197" t="s">
         <v>16</v>
@@ -20496,7 +20492,7 @@
         <v>13</v>
       </c>
       <c r="K198" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L198" t="s">
         <v>16</v>
@@ -20597,7 +20593,7 @@
         <v>13</v>
       </c>
       <c r="K199" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L199" t="s">
         <v>16</v>
@@ -20698,7 +20694,7 @@
         <v>13</v>
       </c>
       <c r="K200" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L200" t="s">
         <v>16</v>
@@ -20799,7 +20795,7 @@
         <v>13</v>
       </c>
       <c r="K201" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L201" t="s">
         <v>16</v>
@@ -20900,7 +20896,7 @@
         <v>13</v>
       </c>
       <c r="K202" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L202" t="s">
         <v>16</v>
@@ -21001,7 +20997,7 @@
         <v>13</v>
       </c>
       <c r="K203" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L203" t="s">
         <v>16</v>
@@ -21102,7 +21098,7 @@
         <v>13</v>
       </c>
       <c r="K204" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L204" t="s">
         <v>16</v>
@@ -21203,7 +21199,7 @@
         <v>13</v>
       </c>
       <c r="K205" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L205" t="s">
         <v>16</v>
@@ -21304,7 +21300,7 @@
         <v>13</v>
       </c>
       <c r="K206" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L206" t="s">
         <v>16</v>
@@ -21405,7 +21401,7 @@
         <v>13</v>
       </c>
       <c r="K207" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L207" t="s">
         <v>16</v>
@@ -21506,7 +21502,7 @@
         <v>13</v>
       </c>
       <c r="K208" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L208" t="s">
         <v>16</v>
@@ -21607,7 +21603,7 @@
         <v>13</v>
       </c>
       <c r="K209" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L209" t="s">
         <v>16</v>
@@ -21708,7 +21704,7 @@
         <v>13</v>
       </c>
       <c r="K210" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L210" t="s">
         <v>16</v>
@@ -21809,7 +21805,7 @@
         <v>13</v>
       </c>
       <c r="K211" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L211" t="s">
         <v>16</v>
@@ -21910,7 +21906,7 @@
         <v>13</v>
       </c>
       <c r="K212" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L212" t="s">
         <v>16</v>
@@ -22011,7 +22007,7 @@
         <v>13</v>
       </c>
       <c r="K213" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L213" t="s">
         <v>16</v>
@@ -22112,7 +22108,7 @@
         <v>13</v>
       </c>
       <c r="K214" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L214" t="s">
         <v>16</v>
@@ -22213,7 +22209,7 @@
         <v>13</v>
       </c>
       <c r="K215" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L215" t="s">
         <v>16</v>
@@ -22314,7 +22310,7 @@
         <v>13</v>
       </c>
       <c r="K216" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L216" t="s">
         <v>16</v>
@@ -22415,7 +22411,7 @@
         <v>13</v>
       </c>
       <c r="K217" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L217" t="s">
         <v>16</v>
@@ -22516,7 +22512,7 @@
         <v>13</v>
       </c>
       <c r="K218" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L218" t="s">
         <v>16</v>
@@ -22617,7 +22613,7 @@
         <v>13</v>
       </c>
       <c r="K219" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L219" t="s">
         <v>16</v>
@@ -22718,7 +22714,7 @@
         <v>13</v>
       </c>
       <c r="K220" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L220" t="s">
         <v>16</v>
@@ -22819,7 +22815,7 @@
         <v>13</v>
       </c>
       <c r="K221" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L221" t="s">
         <v>16</v>
@@ -22920,7 +22916,7 @@
         <v>13</v>
       </c>
       <c r="K222" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L222" t="s">
         <v>16</v>
@@ -23021,7 +23017,7 @@
         <v>13</v>
       </c>
       <c r="K223" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L223" t="s">
         <v>16</v>
@@ -23122,7 +23118,7 @@
         <v>13</v>
       </c>
       <c r="K224" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L224" t="s">
         <v>16</v>
@@ -23223,7 +23219,7 @@
         <v>13</v>
       </c>
       <c r="K225" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L225" t="s">
         <v>16</v>
@@ -23324,7 +23320,7 @@
         <v>13</v>
       </c>
       <c r="K226" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L226" t="s">
         <v>16</v>
@@ -23425,7 +23421,7 @@
         <v>13</v>
       </c>
       <c r="K227" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L227" t="s">
         <v>16</v>
@@ -23526,7 +23522,7 @@
         <v>13</v>
       </c>
       <c r="K228" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L228" t="s">
         <v>16</v>
@@ -23627,7 +23623,7 @@
         <v>13</v>
       </c>
       <c r="K229" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L229" t="s">
         <v>16</v>
@@ -23728,7 +23724,7 @@
         <v>13</v>
       </c>
       <c r="K230" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L230" t="s">
         <v>16</v>
@@ -23829,7 +23825,7 @@
         <v>13</v>
       </c>
       <c r="K231" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L231" t="s">
         <v>16</v>
@@ -23930,7 +23926,7 @@
         <v>13</v>
       </c>
       <c r="K232" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L232" t="s">
         <v>16</v>
@@ -24031,7 +24027,7 @@
         <v>13</v>
       </c>
       <c r="K233" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L233" t="s">
         <v>16</v>
@@ -24132,7 +24128,7 @@
         <v>13</v>
       </c>
       <c r="K234" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L234" t="s">
         <v>16</v>
@@ -24233,7 +24229,7 @@
         <v>13</v>
       </c>
       <c r="K235" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L235" t="s">
         <v>16</v>
@@ -24334,7 +24330,7 @@
         <v>13</v>
       </c>
       <c r="K236" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L236" t="s">
         <v>16</v>
@@ -24435,7 +24431,7 @@
         <v>13</v>
       </c>
       <c r="K237" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L237" t="s">
         <v>16</v>
@@ -24536,7 +24532,7 @@
         <v>13</v>
       </c>
       <c r="K238" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L238" t="s">
         <v>16</v>
@@ -24637,7 +24633,7 @@
         <v>13</v>
       </c>
       <c r="K239" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L239" t="s">
         <v>16</v>
@@ -24738,7 +24734,7 @@
         <v>13</v>
       </c>
       <c r="K240" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L240" t="s">
         <v>16</v>
@@ -24839,7 +24835,7 @@
         <v>13</v>
       </c>
       <c r="K241" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L241" t="s">
         <v>16</v>
@@ -24940,7 +24936,7 @@
         <v>13</v>
       </c>
       <c r="K242" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L242" t="s">
         <v>16</v>
@@ -25041,7 +25037,7 @@
         <v>13</v>
       </c>
       <c r="K243" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L243" t="s">
         <v>16</v>
@@ -25142,7 +25138,7 @@
         <v>13</v>
       </c>
       <c r="K244" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L244" t="s">
         <v>16</v>
@@ -25243,7 +25239,7 @@
         <v>13</v>
       </c>
       <c r="K245" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L245" t="s">
         <v>16</v>
@@ -25344,7 +25340,7 @@
         <v>13</v>
       </c>
       <c r="K246" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L246" t="s">
         <v>16</v>
@@ -25445,7 +25441,7 @@
         <v>13</v>
       </c>
       <c r="K247" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L247" t="s">
         <v>16</v>
@@ -25546,7 +25542,7 @@
         <v>13</v>
       </c>
       <c r="K248" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L248" t="s">
         <v>16</v>
@@ -25647,7 +25643,7 @@
         <v>13</v>
       </c>
       <c r="K249" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L249" t="s">
         <v>16</v>
@@ -25748,7 +25744,7 @@
         <v>13</v>
       </c>
       <c r="K250" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L250" t="s">
         <v>16</v>
@@ -25849,7 +25845,7 @@
         <v>13</v>
       </c>
       <c r="K251" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L251" t="s">
         <v>16</v>
@@ -25950,7 +25946,7 @@
         <v>13</v>
       </c>
       <c r="K252" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L252" t="s">
         <v>16</v>
@@ -26051,7 +26047,7 @@
         <v>13</v>
       </c>
       <c r="K253" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L253" t="s">
         <v>16</v>
@@ -26152,7 +26148,7 @@
         <v>13</v>
       </c>
       <c r="K254" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L254" t="s">
         <v>16</v>
@@ -26253,7 +26249,7 @@
         <v>13</v>
       </c>
       <c r="K255" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L255" t="s">
         <v>16</v>
@@ -26354,7 +26350,7 @@
         <v>13</v>
       </c>
       <c r="K256" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L256" t="s">
         <v>16</v>
@@ -26455,7 +26451,7 @@
         <v>13</v>
       </c>
       <c r="K257" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L257" t="s">
         <v>16</v>
@@ -26556,7 +26552,7 @@
         <v>13</v>
       </c>
       <c r="K258" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L258" t="s">
         <v>16</v>
@@ -26657,7 +26653,7 @@
         <v>13</v>
       </c>
       <c r="K259" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L259" t="s">
         <v>16</v>
@@ -26758,7 +26754,7 @@
         <v>13</v>
       </c>
       <c r="K260" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L260" t="s">
         <v>16</v>
@@ -26859,7 +26855,7 @@
         <v>13</v>
       </c>
       <c r="K261" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L261" t="s">
         <v>16</v>
@@ -26960,7 +26956,7 @@
         <v>13</v>
       </c>
       <c r="K262" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L262" t="s">
         <v>16</v>
@@ -27061,7 +27057,7 @@
         <v>13</v>
       </c>
       <c r="K263" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L263" t="s">
         <v>16</v>
@@ -27162,7 +27158,7 @@
         <v>13</v>
       </c>
       <c r="K264" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L264" t="s">
         <v>16</v>
@@ -27263,7 +27259,7 @@
         <v>13</v>
       </c>
       <c r="K265" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L265" t="s">
         <v>16</v>
@@ -27364,7 +27360,7 @@
         <v>13</v>
       </c>
       <c r="K266" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L266" t="s">
         <v>16</v>
@@ -27465,7 +27461,7 @@
         <v>13</v>
       </c>
       <c r="K267" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L267" t="s">
         <v>16</v>
@@ -27566,7 +27562,7 @@
         <v>13</v>
       </c>
       <c r="K268" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L268" t="s">
         <v>16</v>
@@ -27667,7 +27663,7 @@
         <v>13</v>
       </c>
       <c r="K269" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L269" t="s">
         <v>16</v>
@@ -27768,7 +27764,7 @@
         <v>13</v>
       </c>
       <c r="K270" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L270" t="s">
         <v>16</v>
@@ -27869,7 +27865,7 @@
         <v>13</v>
       </c>
       <c r="K271" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L271" t="s">
         <v>16</v>
@@ -27970,7 +27966,7 @@
         <v>13</v>
       </c>
       <c r="K272" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L272" t="s">
         <v>16</v>
@@ -28071,7 +28067,7 @@
         <v>13</v>
       </c>
       <c r="K273" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L273" t="s">
         <v>16</v>
@@ -28172,7 +28168,7 @@
         <v>13</v>
       </c>
       <c r="K274" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L274" t="s">
         <v>16</v>
@@ -28273,7 +28269,7 @@
         <v>13</v>
       </c>
       <c r="K275" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L275" t="s">
         <v>16</v>
@@ -28374,7 +28370,7 @@
         <v>13</v>
       </c>
       <c r="K276" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L276" t="s">
         <v>16</v>
@@ -28475,7 +28471,7 @@
         <v>13</v>
       </c>
       <c r="K277" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L277" t="s">
         <v>16</v>
@@ -28576,7 +28572,7 @@
         <v>13</v>
       </c>
       <c r="K278" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L278" t="s">
         <v>16</v>
@@ -28677,7 +28673,7 @@
         <v>13</v>
       </c>
       <c r="K279" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L279" t="s">
         <v>16</v>
@@ -28778,7 +28774,7 @@
         <v>13</v>
       </c>
       <c r="K280" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L280" t="s">
         <v>16</v>
@@ -28879,7 +28875,7 @@
         <v>13</v>
       </c>
       <c r="K281" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L281" t="s">
         <v>16</v>
@@ -28980,7 +28976,7 @@
         <v>13</v>
       </c>
       <c r="K282" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L282" t="s">
         <v>16</v>
@@ -29081,7 +29077,7 @@
         <v>13</v>
       </c>
       <c r="K283" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L283" t="s">
         <v>16</v>
@@ -29182,7 +29178,7 @@
         <v>13</v>
       </c>
       <c r="K284" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L284" t="s">
         <v>16</v>
@@ -29283,7 +29279,7 @@
         <v>13</v>
       </c>
       <c r="K285" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L285" t="s">
         <v>16</v>
@@ -29384,7 +29380,7 @@
         <v>13</v>
       </c>
       <c r="K286" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L286" t="s">
         <v>16</v>
@@ -29485,7 +29481,7 @@
         <v>13</v>
       </c>
       <c r="K287" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L287" t="s">
         <v>16</v>
@@ -29586,7 +29582,7 @@
         <v>13</v>
       </c>
       <c r="K288" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L288" t="s">
         <v>16</v>
@@ -29687,7 +29683,7 @@
         <v>13</v>
       </c>
       <c r="K289" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L289" t="s">
         <v>16</v>
@@ -29788,7 +29784,7 @@
         <v>13</v>
       </c>
       <c r="K290" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L290" t="s">
         <v>16</v>
@@ -29889,7 +29885,7 @@
         <v>13</v>
       </c>
       <c r="K291" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L291" t="s">
         <v>16</v>
@@ -29990,7 +29986,7 @@
         <v>13</v>
       </c>
       <c r="K292" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L292" t="s">
         <v>16</v>
@@ -30091,7 +30087,7 @@
         <v>13</v>
       </c>
       <c r="K293" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L293" t="s">
         <v>16</v>
@@ -30192,7 +30188,7 @@
         <v>13</v>
       </c>
       <c r="K294" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L294" t="s">
         <v>16</v>
@@ -30293,7 +30289,7 @@
         <v>13</v>
       </c>
       <c r="K295" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L295" t="s">
         <v>16</v>
@@ -30394,7 +30390,7 @@
         <v>13</v>
       </c>
       <c r="K296" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L296" t="s">
         <v>16</v>
@@ -30495,7 +30491,7 @@
         <v>13</v>
       </c>
       <c r="K297" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L297" t="s">
         <v>16</v>
@@ -30596,7 +30592,7 @@
         <v>13</v>
       </c>
       <c r="K298" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L298" t="s">
         <v>16</v>
@@ -30697,7 +30693,7 @@
         <v>13</v>
       </c>
       <c r="K299" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L299" t="s">
         <v>16</v>
@@ -30798,7 +30794,7 @@
         <v>13</v>
       </c>
       <c r="K300" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L300" t="s">
         <v>16</v>
@@ -30899,7 +30895,7 @@
         <v>13</v>
       </c>
       <c r="K301" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L301" t="s">
         <v>16</v>
@@ -31000,7 +30996,7 @@
         <v>13</v>
       </c>
       <c r="K302" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L302" t="s">
         <v>16</v>
@@ -31101,7 +31097,7 @@
         <v>13</v>
       </c>
       <c r="K303" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L303" t="s">
         <v>16</v>
@@ -31202,7 +31198,7 @@
         <v>13</v>
       </c>
       <c r="K304" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L304" t="s">
         <v>16</v>
@@ -31303,7 +31299,7 @@
         <v>13</v>
       </c>
       <c r="K305" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L305" t="s">
         <v>16</v>
@@ -31404,7 +31400,7 @@
         <v>13</v>
       </c>
       <c r="K306" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L306" t="s">
         <v>16</v>
@@ -31505,7 +31501,7 @@
         <v>13</v>
       </c>
       <c r="K307" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L307" t="s">
         <v>16</v>
@@ -31606,7 +31602,7 @@
         <v>13</v>
       </c>
       <c r="K308" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L308" t="s">
         <v>16</v>
@@ -31707,7 +31703,7 @@
         <v>13</v>
       </c>
       <c r="K309" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L309" t="s">
         <v>16</v>
@@ -31808,7 +31804,7 @@
         <v>13</v>
       </c>
       <c r="K310" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L310" t="s">
         <v>16</v>
@@ -31909,7 +31905,7 @@
         <v>13</v>
       </c>
       <c r="K311" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L311" t="s">
         <v>16</v>
@@ -32010,7 +32006,7 @@
         <v>13</v>
       </c>
       <c r="K312" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L312" t="s">
         <v>16</v>
@@ -32111,7 +32107,7 @@
         <v>13</v>
       </c>
       <c r="K313" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L313" t="s">
         <v>16</v>
@@ -32212,7 +32208,7 @@
         <v>13</v>
       </c>
       <c r="K314" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L314" t="s">
         <v>16</v>
@@ -32313,7 +32309,7 @@
         <v>13</v>
       </c>
       <c r="K315" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L315" t="s">
         <v>16</v>
@@ -32414,7 +32410,7 @@
         <v>13</v>
       </c>
       <c r="K316" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L316" t="s">
         <v>16</v>
@@ -32515,7 +32511,7 @@
         <v>13</v>
       </c>
       <c r="K317" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L317" t="s">
         <v>16</v>
@@ -32616,7 +32612,7 @@
         <v>13</v>
       </c>
       <c r="K318" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L318" t="s">
         <v>16</v>
@@ -32717,7 +32713,7 @@
         <v>13</v>
       </c>
       <c r="K319" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L319" t="s">
         <v>16</v>
@@ -32818,7 +32814,7 @@
         <v>13</v>
       </c>
       <c r="K320" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L320" t="s">
         <v>16</v>
@@ -32919,7 +32915,7 @@
         <v>13</v>
       </c>
       <c r="K321" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L321" t="s">
         <v>16</v>
@@ -33020,7 +33016,7 @@
         <v>13</v>
       </c>
       <c r="K322" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L322" t="s">
         <v>16</v>
@@ -33121,7 +33117,7 @@
         <v>13</v>
       </c>
       <c r="K323" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L323" t="s">
         <v>16</v>
@@ -33222,7 +33218,7 @@
         <v>13</v>
       </c>
       <c r="K324" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L324" t="s">
         <v>16</v>
@@ -33323,7 +33319,7 @@
         <v>13</v>
       </c>
       <c r="K325" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L325" t="s">
         <v>16</v>
@@ -33424,7 +33420,7 @@
         <v>13</v>
       </c>
       <c r="K326" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L326" t="s">
         <v>16</v>
@@ -33525,7 +33521,7 @@
         <v>13</v>
       </c>
       <c r="K327" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L327" t="s">
         <v>16</v>
@@ -33626,7 +33622,7 @@
         <v>13</v>
       </c>
       <c r="K328" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L328" t="s">
         <v>16</v>
@@ -33727,7 +33723,7 @@
         <v>13</v>
       </c>
       <c r="K329" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L329" t="s">
         <v>16</v>
@@ -33828,7 +33824,7 @@
         <v>13</v>
       </c>
       <c r="K330" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L330" t="s">
         <v>16</v>
@@ -33929,7 +33925,7 @@
         <v>13</v>
       </c>
       <c r="K331" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L331" t="s">
         <v>16</v>
@@ -34030,7 +34026,7 @@
         <v>13</v>
       </c>
       <c r="K332" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L332" t="s">
         <v>16</v>
@@ -34131,7 +34127,7 @@
         <v>13</v>
       </c>
       <c r="K333" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L333" t="s">
         <v>16</v>
@@ -34232,7 +34228,7 @@
         <v>13</v>
       </c>
       <c r="K334" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L334" t="s">
         <v>16</v>
@@ -34333,7 +34329,7 @@
         <v>13</v>
       </c>
       <c r="K335" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L335" t="s">
         <v>16</v>
@@ -34434,7 +34430,7 @@
         <v>13</v>
       </c>
       <c r="K336" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L336" t="s">
         <v>16</v>
@@ -34535,7 +34531,7 @@
         <v>13</v>
       </c>
       <c r="K337" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L337" t="s">
         <v>16</v>
@@ -34636,7 +34632,7 @@
         <v>13</v>
       </c>
       <c r="K338" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L338" t="s">
         <v>16</v>
@@ -34737,7 +34733,7 @@
         <v>13</v>
       </c>
       <c r="K339" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L339" t="s">
         <v>16</v>
@@ -34838,7 +34834,7 @@
         <v>13</v>
       </c>
       <c r="K340" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L340" t="s">
         <v>16</v>
@@ -34939,7 +34935,7 @@
         <v>13</v>
       </c>
       <c r="K341" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L341" t="s">
         <v>16</v>
@@ -35040,7 +35036,7 @@
         <v>13</v>
       </c>
       <c r="K342" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L342" t="s">
         <v>16</v>
@@ -35141,7 +35137,7 @@
         <v>13</v>
       </c>
       <c r="K343" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L343" t="s">
         <v>16</v>
@@ -35242,7 +35238,7 @@
         <v>13</v>
       </c>
       <c r="K344" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L344" t="s">
         <v>16</v>
@@ -35343,7 +35339,7 @@
         <v>13</v>
       </c>
       <c r="K345" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L345" t="s">
         <v>16</v>
@@ -35444,7 +35440,7 @@
         <v>13</v>
       </c>
       <c r="K346" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L346" t="s">
         <v>16</v>
@@ -35545,7 +35541,7 @@
         <v>13</v>
       </c>
       <c r="K347" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L347" t="s">
         <v>16</v>
@@ -35646,7 +35642,7 @@
         <v>13</v>
       </c>
       <c r="K348" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L348" t="s">
         <v>16</v>
@@ -35747,7 +35743,7 @@
         <v>13</v>
       </c>
       <c r="K349" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L349" t="s">
         <v>16</v>
@@ -35848,7 +35844,7 @@
         <v>13</v>
       </c>
       <c r="K350" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L350" t="s">
         <v>16</v>
@@ -35949,7 +35945,7 @@
         <v>13</v>
       </c>
       <c r="K351" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L351" t="s">
         <v>16</v>
@@ -36050,7 +36046,7 @@
         <v>13</v>
       </c>
       <c r="K352" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L352" t="s">
         <v>16</v>
@@ -36151,7 +36147,7 @@
         <v>13</v>
       </c>
       <c r="K353" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L353" t="s">
         <v>16</v>
@@ -36252,7 +36248,7 @@
         <v>13</v>
       </c>
       <c r="K354" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L354" t="s">
         <v>16</v>
@@ -36353,7 +36349,7 @@
         <v>13</v>
       </c>
       <c r="K355" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L355" t="s">
         <v>16</v>
@@ -36454,7 +36450,7 @@
         <v>13</v>
       </c>
       <c r="K356" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L356" t="s">
         <v>16</v>
@@ -36555,7 +36551,7 @@
         <v>13</v>
       </c>
       <c r="K357" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L357" t="s">
         <v>16</v>
@@ -36656,7 +36652,7 @@
         <v>13</v>
       </c>
       <c r="K358" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L358" t="s">
         <v>16</v>
@@ -36757,7 +36753,7 @@
         <v>13</v>
       </c>
       <c r="K359" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L359" t="s">
         <v>16</v>
@@ -36858,7 +36854,7 @@
         <v>13</v>
       </c>
       <c r="K360" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L360" t="s">
         <v>16</v>
@@ -36959,7 +36955,7 @@
         <v>13</v>
       </c>
       <c r="K361" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L361" t="s">
         <v>16</v>
@@ -37060,7 +37056,7 @@
         <v>13</v>
       </c>
       <c r="K362" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L362" t="s">
         <v>16</v>
@@ -37161,7 +37157,7 @@
         <v>13</v>
       </c>
       <c r="K363" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L363" t="s">
         <v>16</v>
@@ -37262,7 +37258,7 @@
         <v>13</v>
       </c>
       <c r="K364" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L364" t="s">
         <v>16</v>
@@ -37363,7 +37359,7 @@
         <v>13</v>
       </c>
       <c r="K365" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L365" t="s">
         <v>16</v>
@@ -37464,7 +37460,7 @@
         <v>13</v>
       </c>
       <c r="K366" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L366" t="s">
         <v>16</v>
@@ -37565,7 +37561,7 @@
         <v>13</v>
       </c>
       <c r="K367" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L367" t="s">
         <v>16</v>
@@ -37666,7 +37662,7 @@
         <v>13</v>
       </c>
       <c r="K368" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L368" t="s">
         <v>16</v>
@@ -37767,7 +37763,7 @@
         <v>13</v>
       </c>
       <c r="K369" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L369" t="s">
         <v>16</v>
@@ -37868,7 +37864,7 @@
         <v>13</v>
       </c>
       <c r="K370" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L370" t="s">
         <v>16</v>
@@ -37969,7 +37965,7 @@
         <v>13</v>
       </c>
       <c r="K371" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L371" t="s">
         <v>16</v>
@@ -38070,7 +38066,7 @@
         <v>13</v>
       </c>
       <c r="K372" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L372" t="s">
         <v>16</v>
@@ -38171,7 +38167,7 @@
         <v>13</v>
       </c>
       <c r="K373" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L373" t="s">
         <v>16</v>
@@ -38272,7 +38268,7 @@
         <v>13</v>
       </c>
       <c r="K374" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L374" t="s">
         <v>16</v>
@@ -38373,7 +38369,7 @@
         <v>13</v>
       </c>
       <c r="K375" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L375" t="s">
         <v>16</v>
@@ -38474,7 +38470,7 @@
         <v>13</v>
       </c>
       <c r="K376" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L376" t="s">
         <v>16</v>
@@ -38575,7 +38571,7 @@
         <v>13</v>
       </c>
       <c r="K377" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L377" t="s">
         <v>16</v>
@@ -38676,7 +38672,7 @@
         <v>13</v>
       </c>
       <c r="K378" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L378" t="s">
         <v>16</v>
@@ -38777,7 +38773,7 @@
         <v>13</v>
       </c>
       <c r="K379" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L379" t="s">
         <v>16</v>
@@ -38878,7 +38874,7 @@
         <v>13</v>
       </c>
       <c r="K380" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L380" t="s">
         <v>16</v>
@@ -38979,7 +38975,7 @@
         <v>13</v>
       </c>
       <c r="K381" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L381" t="s">
         <v>16</v>
@@ -39080,7 +39076,7 @@
         <v>13</v>
       </c>
       <c r="K382" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L382" t="s">
         <v>16</v>
@@ -39181,7 +39177,7 @@
         <v>13</v>
       </c>
       <c r="K383" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L383" t="s">
         <v>16</v>
@@ -39282,7 +39278,7 @@
         <v>13</v>
       </c>
       <c r="K384" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L384" t="s">
         <v>16</v>
@@ -39383,7 +39379,7 @@
         <v>13</v>
       </c>
       <c r="K385" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L385" t="s">
         <v>16</v>
@@ -39484,7 +39480,7 @@
         <v>13</v>
       </c>
       <c r="K386" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L386" t="s">
         <v>16</v>
@@ -39585,7 +39581,7 @@
         <v>13</v>
       </c>
       <c r="K387" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L387" t="s">
         <v>16</v>
@@ -39686,7 +39682,7 @@
         <v>13</v>
       </c>
       <c r="K388" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L388" t="s">
         <v>16</v>
@@ -39787,7 +39783,7 @@
         <v>13</v>
       </c>
       <c r="K389" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L389" t="s">
         <v>16</v>
@@ -39888,7 +39884,7 @@
         <v>13</v>
       </c>
       <c r="K390" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L390" t="s">
         <v>16</v>
@@ -39989,7 +39985,7 @@
         <v>13</v>
       </c>
       <c r="K391" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L391" t="s">
         <v>16</v>
@@ -40090,7 +40086,7 @@
         <v>13</v>
       </c>
       <c r="K392" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L392" t="s">
         <v>16</v>
@@ -40191,7 +40187,7 @@
         <v>13</v>
       </c>
       <c r="K393" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L393" t="s">
         <v>16</v>
@@ -40292,7 +40288,7 @@
         <v>13</v>
       </c>
       <c r="K394" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L394" t="s">
         <v>16</v>
@@ -40393,7 +40389,7 @@
         <v>13</v>
       </c>
       <c r="K395" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L395" t="s">
         <v>16</v>
@@ -40494,7 +40490,7 @@
         <v>13</v>
       </c>
       <c r="K396" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L396" t="s">
         <v>16</v>
@@ -40595,7 +40591,7 @@
         <v>13</v>
       </c>
       <c r="K397" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L397" t="s">
         <v>16</v>
@@ -40696,7 +40692,7 @@
         <v>13</v>
       </c>
       <c r="K398" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L398" t="s">
         <v>16</v>
@@ -40797,7 +40793,7 @@
         <v>13</v>
       </c>
       <c r="K399" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L399" t="s">
         <v>16</v>
@@ -40898,7 +40894,7 @@
         <v>13</v>
       </c>
       <c r="K400" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L400" t="s">
         <v>16</v>
@@ -40999,7 +40995,7 @@
         <v>13</v>
       </c>
       <c r="K401" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L401" t="s">
         <v>16</v>
@@ -41100,7 +41096,7 @@
         <v>13</v>
       </c>
       <c r="K402" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L402" t="s">
         <v>16</v>
@@ -41201,7 +41197,7 @@
         <v>13</v>
       </c>
       <c r="K403" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L403" t="s">
         <v>16</v>
@@ -41302,7 +41298,7 @@
         <v>13</v>
       </c>
       <c r="K404" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L404" t="s">
         <v>16</v>
@@ -41403,7 +41399,7 @@
         <v>13</v>
       </c>
       <c r="K405" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L405" t="s">
         <v>16</v>
@@ -41504,7 +41500,7 @@
         <v>13</v>
       </c>
       <c r="K406" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L406" t="s">
         <v>16</v>
@@ -41605,7 +41601,7 @@
         <v>13</v>
       </c>
       <c r="K407" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L407" t="s">
         <v>16</v>
@@ -41706,7 +41702,7 @@
         <v>13</v>
       </c>
       <c r="K408" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L408" t="s">
         <v>16</v>
@@ -41807,7 +41803,7 @@
         <v>13</v>
       </c>
       <c r="K409" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L409" t="s">
         <v>16</v>
@@ -41908,7 +41904,7 @@
         <v>13</v>
       </c>
       <c r="K410" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L410" t="s">
         <v>16</v>
@@ -42009,7 +42005,7 @@
         <v>13</v>
       </c>
       <c r="K411" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L411" t="s">
         <v>16</v>
@@ -42110,7 +42106,7 @@
         <v>13</v>
       </c>
       <c r="K412" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L412" t="s">
         <v>16</v>
@@ -42211,7 +42207,7 @@
         <v>13</v>
       </c>
       <c r="K413" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L413" t="s">
         <v>16</v>
@@ -42312,7 +42308,7 @@
         <v>13</v>
       </c>
       <c r="K414" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L414" t="s">
         <v>16</v>
@@ -42413,7 +42409,7 @@
         <v>13</v>
       </c>
       <c r="K415" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L415" t="s">
         <v>16</v>
@@ -42514,7 +42510,7 @@
         <v>13</v>
       </c>
       <c r="K416" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L416" t="s">
         <v>16</v>
@@ -42615,7 +42611,7 @@
         <v>13</v>
       </c>
       <c r="K417" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L417" t="s">
         <v>16</v>
@@ -42716,7 +42712,7 @@
         <v>13</v>
       </c>
       <c r="K418" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L418" t="s">
         <v>16</v>
@@ -42817,7 +42813,7 @@
         <v>13</v>
       </c>
       <c r="K419" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L419" t="s">
         <v>16</v>
@@ -42918,7 +42914,7 @@
         <v>13</v>
       </c>
       <c r="K420" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L420" t="s">
         <v>16</v>
@@ -43019,7 +43015,7 @@
         <v>13</v>
       </c>
       <c r="K421" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L421" t="s">
         <v>16</v>
@@ -43120,7 +43116,7 @@
         <v>13</v>
       </c>
       <c r="K422" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L422" t="s">
         <v>16</v>
@@ -43221,7 +43217,7 @@
         <v>13</v>
       </c>
       <c r="K423" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L423" t="s">
         <v>16</v>
@@ -43322,7 +43318,7 @@
         <v>13</v>
       </c>
       <c r="K424" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L424" t="s">
         <v>16</v>
@@ -43423,7 +43419,7 @@
         <v>13</v>
       </c>
       <c r="K425" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L425" t="s">
         <v>16</v>
@@ -43524,7 +43520,7 @@
         <v>13</v>
       </c>
       <c r="K426" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L426" t="s">
         <v>16</v>
@@ -43625,7 +43621,7 @@
         <v>13</v>
       </c>
       <c r="K427" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L427" t="s">
         <v>16</v>
@@ -43726,7 +43722,7 @@
         <v>13</v>
       </c>
       <c r="K428" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L428" t="s">
         <v>16</v>
@@ -43827,7 +43823,7 @@
         <v>13</v>
       </c>
       <c r="K429" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L429" t="s">
         <v>16</v>
@@ -43928,7 +43924,7 @@
         <v>13</v>
       </c>
       <c r="K430" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L430" t="s">
         <v>16</v>
@@ -44029,7 +44025,7 @@
         <v>13</v>
       </c>
       <c r="K431" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L431" t="s">
         <v>16</v>
@@ -44130,7 +44126,7 @@
         <v>13</v>
       </c>
       <c r="K432" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L432" t="s">
         <v>16</v>
@@ -44231,7 +44227,7 @@
         <v>13</v>
       </c>
       <c r="K433" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L433" t="s">
         <v>16</v>
@@ -44332,7 +44328,7 @@
         <v>13</v>
       </c>
       <c r="K434" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L434" t="s">
         <v>16</v>
@@ -44433,7 +44429,7 @@
         <v>13</v>
       </c>
       <c r="K435" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L435" t="s">
         <v>16</v>
@@ -44534,7 +44530,7 @@
         <v>13</v>
       </c>
       <c r="K436" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L436" t="s">
         <v>16</v>
@@ -44635,7 +44631,7 @@
         <v>13</v>
       </c>
       <c r="K437" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L437" t="s">
         <v>16</v>
@@ -44736,7 +44732,7 @@
         <v>13</v>
       </c>
       <c r="K438" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L438" t="s">
         <v>16</v>
@@ -44837,7 +44833,7 @@
         <v>13</v>
       </c>
       <c r="K439" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L439" t="s">
         <v>16</v>
@@ -44938,7 +44934,7 @@
         <v>13</v>
       </c>
       <c r="K440" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L440" t="s">
         <v>16</v>
@@ -45039,7 +45035,7 @@
         <v>13</v>
       </c>
       <c r="K441" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L441" t="s">
         <v>16</v>
@@ -45140,7 +45136,7 @@
         <v>13</v>
       </c>
       <c r="K442" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L442" t="s">
         <v>16</v>
@@ -45211,7 +45207,7 @@
     </row>
     <row r="443" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B443">
         <v>442</v>
@@ -45241,7 +45237,7 @@
         <v>13</v>
       </c>
       <c r="K443" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L443" t="s">
         <v>16</v>
@@ -45342,7 +45338,7 @@
         <v>13</v>
       </c>
       <c r="K444" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L444" t="s">
         <v>16</v>
@@ -45443,7 +45439,7 @@
         <v>13</v>
       </c>
       <c r="K445" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L445" t="s">
         <v>16</v>
@@ -45544,7 +45540,7 @@
         <v>13</v>
       </c>
       <c r="K446" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L446" t="s">
         <v>16</v>
@@ -45645,7 +45641,7 @@
         <v>13</v>
       </c>
       <c r="K447" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L447" t="s">
         <v>16</v>
@@ -45746,7 +45742,7 @@
         <v>13</v>
       </c>
       <c r="K448" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L448" t="s">
         <v>16</v>
@@ -45847,7 +45843,7 @@
         <v>13</v>
       </c>
       <c r="K449" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L449" t="s">
         <v>16</v>
@@ -45948,7 +45944,7 @@
         <v>13</v>
       </c>
       <c r="K450" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L450" t="s">
         <v>16</v>
@@ -46049,7 +46045,7 @@
         <v>13</v>
       </c>
       <c r="K451" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L451" t="s">
         <v>16</v>
@@ -46150,7 +46146,7 @@
         <v>13</v>
       </c>
       <c r="K452" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L452" t="s">
         <v>16</v>
@@ -46251,7 +46247,7 @@
         <v>13</v>
       </c>
       <c r="K453" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L453" t="s">
         <v>16</v>
@@ -46352,7 +46348,7 @@
         <v>13</v>
       </c>
       <c r="K454" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L454" t="s">
         <v>16</v>
@@ -46453,7 +46449,7 @@
         <v>13</v>
       </c>
       <c r="K455" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L455" t="s">
         <v>16</v>
@@ -46554,7 +46550,7 @@
         <v>13</v>
       </c>
       <c r="K456" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L456" t="s">
         <v>16</v>
@@ -46655,7 +46651,7 @@
         <v>13</v>
       </c>
       <c r="K457" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L457" t="s">
         <v>16</v>
@@ -46756,7 +46752,7 @@
         <v>13</v>
       </c>
       <c r="K458" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L458" t="s">
         <v>16</v>
@@ -46857,7 +46853,7 @@
         <v>13</v>
       </c>
       <c r="K459" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L459" t="s">
         <v>16</v>
@@ -46958,7 +46954,7 @@
         <v>13</v>
       </c>
       <c r="K460" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L460" t="s">
         <v>16</v>
@@ -47059,7 +47055,7 @@
         <v>13</v>
       </c>
       <c r="K461" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L461" t="s">
         <v>16</v>
@@ -47160,7 +47156,7 @@
         <v>13</v>
       </c>
       <c r="K462" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L462" t="s">
         <v>16</v>
@@ -47261,7 +47257,7 @@
         <v>13</v>
       </c>
       <c r="K463" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L463" t="s">
         <v>16</v>
@@ -47362,7 +47358,7 @@
         <v>13</v>
       </c>
       <c r="K464" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L464" t="s">
         <v>16</v>
@@ -47463,7 +47459,7 @@
         <v>13</v>
       </c>
       <c r="K465" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L465" t="s">
         <v>16</v>
@@ -47564,7 +47560,7 @@
         <v>13</v>
       </c>
       <c r="K466" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L466" t="s">
         <v>16</v>
@@ -47665,7 +47661,7 @@
         <v>13</v>
       </c>
       <c r="K467" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L467" t="s">
         <v>16</v>
@@ -47766,7 +47762,7 @@
         <v>13</v>
       </c>
       <c r="K468" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L468" t="s">
         <v>16</v>
@@ -47867,7 +47863,7 @@
         <v>13</v>
       </c>
       <c r="K469" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L469" t="s">
         <v>16</v>
@@ -47968,7 +47964,7 @@
         <v>13</v>
       </c>
       <c r="K470" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L470" t="s">
         <v>16</v>
@@ -48069,7 +48065,7 @@
         <v>13</v>
       </c>
       <c r="K471" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L471" t="s">
         <v>16</v>
@@ -48170,7 +48166,7 @@
         <v>13</v>
       </c>
       <c r="K472" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L472" t="s">
         <v>16</v>
@@ -48271,7 +48267,7 @@
         <v>13</v>
       </c>
       <c r="K473" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L473" t="s">
         <v>16</v>
@@ -48372,7 +48368,7 @@
         <v>13</v>
       </c>
       <c r="K474" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L474" t="s">
         <v>16</v>
@@ -48473,7 +48469,7 @@
         <v>13</v>
       </c>
       <c r="K475" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L475" t="s">
         <v>16</v>
@@ -48574,7 +48570,7 @@
         <v>13</v>
       </c>
       <c r="K476" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L476" t="s">
         <v>16</v>
@@ -48675,7 +48671,7 @@
         <v>13</v>
       </c>
       <c r="K477" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L477" t="s">
         <v>16</v>
@@ -48776,7 +48772,7 @@
         <v>13</v>
       </c>
       <c r="K478" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L478" t="s">
         <v>16</v>
@@ -48877,7 +48873,7 @@
         <v>13</v>
       </c>
       <c r="K479" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L479" t="s">
         <v>16</v>
@@ -48978,7 +48974,7 @@
         <v>13</v>
       </c>
       <c r="K480" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L480" t="s">
         <v>16</v>
@@ -49079,7 +49075,7 @@
         <v>13</v>
       </c>
       <c r="K481" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L481" t="s">
         <v>16</v>
@@ -49180,7 +49176,7 @@
         <v>13</v>
       </c>
       <c r="K482" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L482" t="s">
         <v>16</v>
@@ -49281,7 +49277,7 @@
         <v>13</v>
       </c>
       <c r="K483" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L483" t="s">
         <v>16</v>
@@ -49382,7 +49378,7 @@
         <v>13</v>
       </c>
       <c r="K484" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L484" t="s">
         <v>16</v>
@@ -49483,7 +49479,7 @@
         <v>13</v>
       </c>
       <c r="K485" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L485" t="s">
         <v>16</v>
@@ -49584,7 +49580,7 @@
         <v>13</v>
       </c>
       <c r="K486" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L486" t="s">
         <v>16</v>
@@ -49685,7 +49681,7 @@
         <v>13</v>
       </c>
       <c r="K487" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L487" t="s">
         <v>16</v>
@@ -49786,7 +49782,7 @@
         <v>13</v>
       </c>
       <c r="K488" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L488" t="s">
         <v>16</v>
@@ -49887,7 +49883,7 @@
         <v>13</v>
       </c>
       <c r="K489" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L489" t="s">
         <v>16</v>
@@ -49988,7 +49984,7 @@
         <v>13</v>
       </c>
       <c r="K490" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L490" t="s">
         <v>16</v>
@@ -50089,7 +50085,7 @@
         <v>13</v>
       </c>
       <c r="K491" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L491" t="s">
         <v>16</v>
@@ -50190,7 +50186,7 @@
         <v>13</v>
       </c>
       <c r="K492" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L492" t="s">
         <v>16</v>
@@ -50291,7 +50287,7 @@
         <v>13</v>
       </c>
       <c r="K493" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L493" t="s">
         <v>16</v>
@@ -50392,7 +50388,7 @@
         <v>13</v>
       </c>
       <c r="K494" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L494" t="s">
         <v>16</v>
@@ -50493,7 +50489,7 @@
         <v>13</v>
       </c>
       <c r="K495" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L495" t="s">
         <v>16</v>
@@ -50594,7 +50590,7 @@
         <v>13</v>
       </c>
       <c r="K496" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L496" t="s">
         <v>16</v>
@@ -50695,7 +50691,7 @@
         <v>13</v>
       </c>
       <c r="K497" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L497" t="s">
         <v>16</v>
@@ -50796,7 +50792,7 @@
         <v>13</v>
       </c>
       <c r="K498" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L498" t="s">
         <v>16</v>
@@ -50897,7 +50893,7 @@
         <v>13</v>
       </c>
       <c r="K499" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L499" t="s">
         <v>16</v>
@@ -50998,7 +50994,7 @@
         <v>13</v>
       </c>
       <c r="K500" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L500" t="s">
         <v>16</v>
@@ -51099,7 +51095,7 @@
         <v>13</v>
       </c>
       <c r="K501" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L501" t="s">
         <v>16</v>
@@ -51200,7 +51196,7 @@
         <v>13</v>
       </c>
       <c r="K502" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L502" t="s">
         <v>16</v>
@@ -51301,7 +51297,7 @@
         <v>13</v>
       </c>
       <c r="K503" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L503" t="s">
         <v>16</v>
@@ -51402,7 +51398,7 @@
         <v>13</v>
       </c>
       <c r="K504" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L504" t="s">
         <v>16</v>
@@ -51503,7 +51499,7 @@
         <v>13</v>
       </c>
       <c r="K505" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L505" t="s">
         <v>16</v>
@@ -51604,7 +51600,7 @@
         <v>13</v>
       </c>
       <c r="K506" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L506" t="s">
         <v>16</v>
@@ -51705,7 +51701,7 @@
         <v>13</v>
       </c>
       <c r="K507" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L507" t="s">
         <v>16</v>
@@ -51806,7 +51802,7 @@
         <v>13</v>
       </c>
       <c r="K508" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L508" t="s">
         <v>16</v>
@@ -51907,7 +51903,7 @@
         <v>13</v>
       </c>
       <c r="K509" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L509" t="s">
         <v>16</v>
@@ -52008,7 +52004,7 @@
         <v>13</v>
       </c>
       <c r="K510" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L510" t="s">
         <v>16</v>
@@ -52109,7 +52105,7 @@
         <v>13</v>
       </c>
       <c r="K511" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L511" t="s">
         <v>16</v>
@@ -52210,7 +52206,7 @@
         <v>13</v>
       </c>
       <c r="K512" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L512" t="s">
         <v>16</v>
@@ -52311,7 +52307,7 @@
         <v>13</v>
       </c>
       <c r="K513" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L513" t="s">
         <v>16</v>
@@ -52412,7 +52408,7 @@
         <v>13</v>
       </c>
       <c r="K514" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L514" t="s">
         <v>16</v>
@@ -52513,7 +52509,7 @@
         <v>13</v>
       </c>
       <c r="K515" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L515" t="s">
         <v>16</v>
@@ -52614,7 +52610,7 @@
         <v>13</v>
       </c>
       <c r="K516" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L516" t="s">
         <v>16</v>
@@ -52715,7 +52711,7 @@
         <v>13</v>
       </c>
       <c r="K517" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L517" t="s">
         <v>16</v>
@@ -52816,7 +52812,7 @@
         <v>13</v>
       </c>
       <c r="K518" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L518" t="s">
         <v>16</v>
@@ -52917,7 +52913,7 @@
         <v>13</v>
       </c>
       <c r="K519" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L519" t="s">
         <v>16</v>
@@ -53018,7 +53014,7 @@
         <v>13</v>
       </c>
       <c r="K520" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L520" t="s">
         <v>16</v>
@@ -53119,7 +53115,7 @@
         <v>13</v>
       </c>
       <c r="K521" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L521" t="s">
         <v>16</v>
@@ -53220,7 +53216,7 @@
         <v>13</v>
       </c>
       <c r="K522" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L522" t="s">
         <v>16</v>
@@ -53321,7 +53317,7 @@
         <v>13</v>
       </c>
       <c r="K523" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L523" t="s">
         <v>16</v>
@@ -53422,7 +53418,7 @@
         <v>13</v>
       </c>
       <c r="K524" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L524" t="s">
         <v>16</v>
@@ -53523,7 +53519,7 @@
         <v>13</v>
       </c>
       <c r="K525" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L525" t="s">
         <v>16</v>
@@ -53624,7 +53620,7 @@
         <v>13</v>
       </c>
       <c r="K526" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L526" t="s">
         <v>16</v>
@@ -53725,7 +53721,7 @@
         <v>13</v>
       </c>
       <c r="K527" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L527" t="s">
         <v>16</v>
@@ -53826,7 +53822,7 @@
         <v>13</v>
       </c>
       <c r="K528" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L528" t="s">
         <v>16</v>
@@ -53927,7 +53923,7 @@
         <v>13</v>
       </c>
       <c r="K529" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L529" t="s">
         <v>16</v>
@@ -54028,7 +54024,7 @@
         <v>13</v>
       </c>
       <c r="K530" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L530" t="s">
         <v>16</v>
@@ -54129,7 +54125,7 @@
         <v>13</v>
       </c>
       <c r="K531" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L531" t="s">
         <v>16</v>
@@ -54230,7 +54226,7 @@
         <v>13</v>
       </c>
       <c r="K532" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L532" t="s">
         <v>16</v>
@@ -54331,7 +54327,7 @@
         <v>13</v>
       </c>
       <c r="K533" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L533" t="s">
         <v>16</v>
@@ -54432,7 +54428,7 @@
         <v>13</v>
       </c>
       <c r="K534" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L534" t="s">
         <v>16</v>
@@ -54533,7 +54529,7 @@
         <v>13</v>
       </c>
       <c r="K535" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L535" t="s">
         <v>16</v>
@@ -54634,7 +54630,7 @@
         <v>13</v>
       </c>
       <c r="K536" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L536" t="s">
         <v>16</v>
@@ -54735,7 +54731,7 @@
         <v>13</v>
       </c>
       <c r="K537" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L537" t="s">
         <v>16</v>
@@ -54836,7 +54832,7 @@
         <v>13</v>
       </c>
       <c r="K538" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L538" t="s">
         <v>16</v>
@@ -54937,7 +54933,7 @@
         <v>13</v>
       </c>
       <c r="K539" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L539" t="s">
         <v>16</v>
@@ -55038,7 +55034,7 @@
         <v>13</v>
       </c>
       <c r="K540" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L540" t="s">
         <v>16</v>
@@ -55139,7 +55135,7 @@
         <v>13</v>
       </c>
       <c r="K541" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L541" t="s">
         <v>16</v>
@@ -55240,7 +55236,7 @@
         <v>13</v>
       </c>
       <c r="K542" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L542" t="s">
         <v>16</v>
@@ -55341,7 +55337,7 @@
         <v>13</v>
       </c>
       <c r="K543" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L543" t="s">
         <v>16</v>
@@ -55442,7 +55438,7 @@
         <v>13</v>
       </c>
       <c r="K544" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L544" t="s">
         <v>16</v>
@@ -55543,7 +55539,7 @@
         <v>13</v>
       </c>
       <c r="K545" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L545" t="s">
         <v>16</v>
@@ -55644,7 +55640,7 @@
         <v>13</v>
       </c>
       <c r="K546" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L546" t="s">
         <v>16</v>
@@ -55745,7 +55741,7 @@
         <v>13</v>
       </c>
       <c r="K547" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L547" t="s">
         <v>16</v>
@@ -55846,7 +55842,7 @@
         <v>13</v>
       </c>
       <c r="K548" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L548" t="s">
         <v>16</v>
@@ -55947,7 +55943,7 @@
         <v>13</v>
       </c>
       <c r="K549" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L549" t="s">
         <v>16</v>
@@ -56048,7 +56044,7 @@
         <v>13</v>
       </c>
       <c r="K550" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L550" t="s">
         <v>16</v>
@@ -56149,7 +56145,7 @@
         <v>13</v>
       </c>
       <c r="K551" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L551" t="s">
         <v>16</v>
@@ -56250,7 +56246,7 @@
         <v>13</v>
       </c>
       <c r="K552" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L552" t="s">
         <v>16</v>
@@ -56351,7 +56347,7 @@
         <v>13</v>
       </c>
       <c r="K553" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L553" t="s">
         <v>16</v>
@@ -56452,7 +56448,7 @@
         <v>13</v>
       </c>
       <c r="K554" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L554" t="s">
         <v>16</v>
@@ -56553,7 +56549,7 @@
         <v>13</v>
       </c>
       <c r="K555" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L555" t="s">
         <v>16</v>
@@ -56654,7 +56650,7 @@
         <v>13</v>
       </c>
       <c r="K556" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L556" t="s">
         <v>16</v>
@@ -56755,7 +56751,7 @@
         <v>13</v>
       </c>
       <c r="K557" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L557" t="s">
         <v>16</v>
@@ -56856,7 +56852,7 @@
         <v>13</v>
       </c>
       <c r="K558" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L558" t="s">
         <v>16</v>
@@ -56957,7 +56953,7 @@
         <v>13</v>
       </c>
       <c r="K559" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L559" t="s">
         <v>16</v>
@@ -57058,7 +57054,7 @@
         <v>13</v>
       </c>
       <c r="K560" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L560" t="s">
         <v>16</v>
@@ -57159,7 +57155,7 @@
         <v>13</v>
       </c>
       <c r="K561" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L561" t="s">
         <v>16</v>
@@ -57260,7 +57256,7 @@
         <v>13</v>
       </c>
       <c r="K562" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L562" t="s">
         <v>16</v>
@@ -57361,7 +57357,7 @@
         <v>13</v>
       </c>
       <c r="K563" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L563" t="s">
         <v>16</v>
@@ -57462,7 +57458,7 @@
         <v>13</v>
       </c>
       <c r="K564" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L564" t="s">
         <v>16</v>
@@ -57563,7 +57559,7 @@
         <v>13</v>
       </c>
       <c r="K565" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L565" t="s">
         <v>16</v>
@@ -57664,7 +57660,7 @@
         <v>13</v>
       </c>
       <c r="K566" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L566" t="s">
         <v>16</v>
@@ -57765,7 +57761,7 @@
         <v>13</v>
       </c>
       <c r="K567" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L567" t="s">
         <v>16</v>
@@ -57866,7 +57862,7 @@
         <v>13</v>
       </c>
       <c r="K568" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L568" t="s">
         <v>16</v>
@@ -57967,7 +57963,7 @@
         <v>13</v>
       </c>
       <c r="K569" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L569" t="s">
         <v>16</v>
@@ -58068,7 +58064,7 @@
         <v>13</v>
       </c>
       <c r="K570" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L570" t="s">
         <v>16</v>
@@ -58169,7 +58165,7 @@
         <v>13</v>
       </c>
       <c r="K571" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L571" t="s">
         <v>16</v>
@@ -58270,7 +58266,7 @@
         <v>13</v>
       </c>
       <c r="K572" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L572" t="s">
         <v>16</v>
@@ -58371,7 +58367,7 @@
         <v>13</v>
       </c>
       <c r="K573" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L573" t="s">
         <v>16</v>
@@ -58472,7 +58468,7 @@
         <v>13</v>
       </c>
       <c r="K574" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L574" t="s">
         <v>16</v>
@@ -58573,7 +58569,7 @@
         <v>13</v>
       </c>
       <c r="K575" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L575" t="s">
         <v>16</v>
@@ -58674,7 +58670,7 @@
         <v>13</v>
       </c>
       <c r="K576" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L576" t="s">
         <v>16</v>
@@ -58775,7 +58771,7 @@
         <v>13</v>
       </c>
       <c r="K577" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L577" t="s">
         <v>16</v>
@@ -58876,7 +58872,7 @@
         <v>13</v>
       </c>
       <c r="K578" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L578" t="s">
         <v>16</v>
@@ -58977,7 +58973,7 @@
         <v>13</v>
       </c>
       <c r="K579" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L579" t="s">
         <v>16</v>
@@ -59078,7 +59074,7 @@
         <v>13</v>
       </c>
       <c r="K580" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L580" t="s">
         <v>16</v>
@@ -59179,7 +59175,7 @@
         <v>13</v>
       </c>
       <c r="K581" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L581" t="s">
         <v>16</v>
@@ -59280,7 +59276,7 @@
         <v>13</v>
       </c>
       <c r="K582" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L582" t="s">
         <v>16</v>
@@ -59381,7 +59377,7 @@
         <v>13</v>
       </c>
       <c r="K583" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L583" t="s">
         <v>16</v>
@@ -59482,7 +59478,7 @@
         <v>13</v>
       </c>
       <c r="K584" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L584" t="s">
         <v>16</v>
@@ -59583,7 +59579,7 @@
         <v>13</v>
       </c>
       <c r="K585" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L585" t="s">
         <v>16</v>
@@ -59684,7 +59680,7 @@
         <v>13</v>
       </c>
       <c r="K586" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L586" t="s">
         <v>16</v>
@@ -59785,7 +59781,7 @@
         <v>13</v>
       </c>
       <c r="K587" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L587" t="s">
         <v>16</v>
@@ -59886,7 +59882,7 @@
         <v>13</v>
       </c>
       <c r="K588" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L588" t="s">
         <v>16</v>
@@ -59987,7 +59983,7 @@
         <v>13</v>
       </c>
       <c r="K589" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L589" t="s">
         <v>16</v>
@@ -60088,7 +60084,7 @@
         <v>13</v>
       </c>
       <c r="K590" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L590" t="s">
         <v>16</v>
@@ -60189,7 +60185,7 @@
         <v>13</v>
       </c>
       <c r="K591" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L591" t="s">
         <v>16</v>
@@ -60290,7 +60286,7 @@
         <v>13</v>
       </c>
       <c r="K592" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L592" t="s">
         <v>16</v>
@@ -60391,7 +60387,7 @@
         <v>13</v>
       </c>
       <c r="K593" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L593" t="s">
         <v>16</v>
@@ -60492,7 +60488,7 @@
         <v>13</v>
       </c>
       <c r="K594" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L594" t="s">
         <v>16</v>
@@ -60593,7 +60589,7 @@
         <v>13</v>
       </c>
       <c r="K595" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L595" t="s">
         <v>16</v>
@@ -60694,7 +60690,7 @@
         <v>13</v>
       </c>
       <c r="K596" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L596" t="s">
         <v>16</v>
@@ -60795,7 +60791,7 @@
         <v>13</v>
       </c>
       <c r="K597" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L597" t="s">
         <v>16</v>
@@ -60896,7 +60892,7 @@
         <v>13</v>
       </c>
       <c r="K598" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L598" t="s">
         <v>16</v>
@@ -60997,7 +60993,7 @@
         <v>13</v>
       </c>
       <c r="K599" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L599" t="s">
         <v>16</v>
@@ -61098,7 +61094,7 @@
         <v>13</v>
       </c>
       <c r="K600" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L600" t="s">
         <v>16</v>
@@ -61199,7 +61195,7 @@
         <v>13</v>
       </c>
       <c r="K601" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L601" t="s">
         <v>16</v>
@@ -61300,7 +61296,7 @@
         <v>13</v>
       </c>
       <c r="K602" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L602" t="s">
         <v>16</v>
@@ -61401,7 +61397,7 @@
         <v>13</v>
       </c>
       <c r="K603" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L603" t="s">
         <v>16</v>
@@ -61502,7 +61498,7 @@
         <v>13</v>
       </c>
       <c r="K604" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L604" t="s">
         <v>16</v>
@@ -61603,7 +61599,7 @@
         <v>13</v>
       </c>
       <c r="K605" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L605" t="s">
         <v>16</v>
@@ -61704,7 +61700,7 @@
         <v>13</v>
       </c>
       <c r="K606" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L606" t="s">
         <v>16</v>
@@ -61805,7 +61801,7 @@
         <v>13</v>
       </c>
       <c r="K607" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L607" t="s">
         <v>16</v>
@@ -61906,7 +61902,7 @@
         <v>13</v>
       </c>
       <c r="K608" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L608" t="s">
         <v>16</v>
@@ -62007,7 +62003,7 @@
         <v>13</v>
       </c>
       <c r="K609" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L609" t="s">
         <v>16</v>
@@ -62108,7 +62104,7 @@
         <v>13</v>
       </c>
       <c r="K610" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L610" t="s">
         <v>16</v>
@@ -62209,7 +62205,7 @@
         <v>13</v>
       </c>
       <c r="K611" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L611" t="s">
         <v>16</v>
@@ -62310,7 +62306,7 @@
         <v>13</v>
       </c>
       <c r="K612" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L612" t="s">
         <v>16</v>
@@ -62411,7 +62407,7 @@
         <v>13</v>
       </c>
       <c r="K613" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L613" t="s">
         <v>16</v>
@@ -62512,7 +62508,7 @@
         <v>13</v>
       </c>
       <c r="K614" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L614" t="s">
         <v>16</v>
@@ -62613,7 +62609,7 @@
         <v>13</v>
       </c>
       <c r="K615" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L615" t="s">
         <v>16</v>
@@ -62714,7 +62710,7 @@
         <v>13</v>
       </c>
       <c r="K616" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L616" t="s">
         <v>16</v>
@@ -62815,7 +62811,7 @@
         <v>13</v>
       </c>
       <c r="K617" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L617" t="s">
         <v>16</v>
@@ -62916,7 +62912,7 @@
         <v>13</v>
       </c>
       <c r="K618" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L618" t="s">
         <v>16</v>
@@ -63017,7 +63013,7 @@
         <v>13</v>
       </c>
       <c r="K619" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L619" t="s">
         <v>16</v>
@@ -63118,7 +63114,7 @@
         <v>13</v>
       </c>
       <c r="K620" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L620" t="s">
         <v>16</v>
@@ -63219,7 +63215,7 @@
         <v>13</v>
       </c>
       <c r="K621" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L621" t="s">
         <v>16</v>
@@ -63320,7 +63316,7 @@
         <v>13</v>
       </c>
       <c r="K622" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L622" t="s">
         <v>16</v>
@@ -63421,7 +63417,7 @@
         <v>13</v>
       </c>
       <c r="K623" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L623" t="s">
         <v>16</v>
@@ -63522,7 +63518,7 @@
         <v>13</v>
       </c>
       <c r="K624" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L624" t="s">
         <v>16</v>
@@ -63623,7 +63619,7 @@
         <v>13</v>
       </c>
       <c r="K625" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L625" t="s">
         <v>16</v>
@@ -63724,7 +63720,7 @@
         <v>13</v>
       </c>
       <c r="K626" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L626" t="s">
         <v>16</v>
@@ -63825,7 +63821,7 @@
         <v>13</v>
       </c>
       <c r="K627" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L627" t="s">
         <v>16</v>
@@ -63926,7 +63922,7 @@
         <v>13</v>
       </c>
       <c r="K628" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L628" t="s">
         <v>16</v>
@@ -64027,7 +64023,7 @@
         <v>13</v>
       </c>
       <c r="K629" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L629" t="s">
         <v>16</v>
@@ -64128,7 +64124,7 @@
         <v>13</v>
       </c>
       <c r="K630" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L630" t="s">
         <v>16</v>
@@ -64229,7 +64225,7 @@
         <v>13</v>
       </c>
       <c r="K631" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L631" t="s">
         <v>16</v>
@@ -64330,7 +64326,7 @@
         <v>13</v>
       </c>
       <c r="K632" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L632" t="s">
         <v>16</v>
@@ -64431,7 +64427,7 @@
         <v>13</v>
       </c>
       <c r="K633" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L633" t="s">
         <v>16</v>
@@ -64532,7 +64528,7 @@
         <v>13</v>
       </c>
       <c r="K634" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L634" t="s">
         <v>16</v>
@@ -64633,7 +64629,7 @@
         <v>13</v>
       </c>
       <c r="K635" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L635" t="s">
         <v>16</v>
@@ -64734,7 +64730,7 @@
         <v>13</v>
       </c>
       <c r="K636" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L636" t="s">
         <v>16</v>
@@ -64835,7 +64831,7 @@
         <v>13</v>
       </c>
       <c r="K637" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L637" t="s">
         <v>16</v>
@@ -64936,7 +64932,7 @@
         <v>13</v>
       </c>
       <c r="K638" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L638" t="s">
         <v>16</v>
@@ -65037,7 +65033,7 @@
         <v>13</v>
       </c>
       <c r="K639" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L639" t="s">
         <v>16</v>
@@ -65138,7 +65134,7 @@
         <v>13</v>
       </c>
       <c r="K640" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L640" t="s">
         <v>16</v>
@@ -65239,7 +65235,7 @@
         <v>13</v>
       </c>
       <c r="K641" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L641" t="s">
         <v>16</v>
@@ -65340,7 +65336,7 @@
         <v>13</v>
       </c>
       <c r="K642" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L642" t="s">
         <v>16</v>
@@ -65441,7 +65437,7 @@
         <v>13</v>
       </c>
       <c r="K643" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L643" t="s">
         <v>16</v>
@@ -65542,7 +65538,7 @@
         <v>13</v>
       </c>
       <c r="K644" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L644" t="s">
         <v>16</v>
@@ -65643,7 +65639,7 @@
         <v>13</v>
       </c>
       <c r="K645" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L645" t="s">
         <v>16</v>
@@ -65744,7 +65740,7 @@
         <v>13</v>
       </c>
       <c r="K646" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L646" t="s">
         <v>16</v>
@@ -65845,7 +65841,7 @@
         <v>13</v>
       </c>
       <c r="K647" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L647" t="s">
         <v>16</v>
@@ -65946,7 +65942,7 @@
         <v>13</v>
       </c>
       <c r="K648" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L648" t="s">
         <v>16</v>
@@ -66047,7 +66043,7 @@
         <v>13</v>
       </c>
       <c r="K649" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L649" t="s">
         <v>16</v>
@@ -66148,7 +66144,7 @@
         <v>13</v>
       </c>
       <c r="K650" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L650" t="s">
         <v>16</v>
@@ -66249,7 +66245,7 @@
         <v>13</v>
       </c>
       <c r="K651" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L651" t="s">
         <v>16</v>
@@ -66350,7 +66346,7 @@
         <v>13</v>
       </c>
       <c r="K652" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L652" t="s">
         <v>16</v>
@@ -66451,7 +66447,7 @@
         <v>13</v>
       </c>
       <c r="K653" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L653" t="s">
         <v>16</v>
@@ -66552,7 +66548,7 @@
         <v>13</v>
       </c>
       <c r="K654" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L654" t="s">
         <v>16</v>
@@ -66653,7 +66649,7 @@
         <v>13</v>
       </c>
       <c r="K655" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L655" t="s">
         <v>16</v>
@@ -66754,7 +66750,7 @@
         <v>13</v>
       </c>
       <c r="K656" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L656" t="s">
         <v>16</v>
@@ -66855,7 +66851,7 @@
         <v>13</v>
       </c>
       <c r="K657" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L657" t="s">
         <v>16</v>
@@ -66956,7 +66952,7 @@
         <v>13</v>
       </c>
       <c r="K658" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L658" t="s">
         <v>16</v>
@@ -67057,7 +67053,7 @@
         <v>13</v>
       </c>
       <c r="K659" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L659" t="s">
         <v>16</v>
@@ -67158,7 +67154,7 @@
         <v>13</v>
       </c>
       <c r="K660" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L660" t="s">
         <v>16</v>
@@ -67259,7 +67255,7 @@
         <v>13</v>
       </c>
       <c r="K661" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L661" t="s">
         <v>16</v>
@@ -67360,7 +67356,7 @@
         <v>13</v>
       </c>
       <c r="K662" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L662" t="s">
         <v>16</v>
